--- a/data_prep/ELSTAT/SBR03_02.xlsx
+++ b/data_prep/ELSTAT/SBR03_02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\0_ΠΕΙΡΑΜΑΤΙΚΕΣ ΣΤΑΤΙΣΤΙΚΕΣ\ΚΑΤΑΛΥΜΑΤΑ ΕΣΤΙΑΣΗ\Q2 2025\ΑΡΧΕΙΑ ΓΙΑ ΑΠΟΣΤΟΛΗ\ΠΙΝΑΚΕΣ ΙΣΤΟΣΕΛΙΔΑΣ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03_ΤΜΗΜΑ ΜΗΤΡΩΩΝ ΚΑΙ ΜΕΓΑΛΩΝ ΕΠΙΧΕΙΡΗΣΕΩΝ\BUSINESS REGISTER\1_PR_COVID_NACE_55_56_2025\Q4_2025\ΠΙΝΑΚΕΣ ΙΣΤΟΣΕΛΙΔΑΣ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC36F16-8AE0-469E-8E24-94EA20BB177B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9AA347-61F3-4A32-952A-7B1B2D8ED414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{8721A59E-3967-4667-9553-B216BCA7C438}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{8721A59E-3967-4667-9553-B216BCA7C438}"/>
   </bookViews>
   <sheets>
     <sheet name="NACE_56_A" sheetId="3" r:id="rId1"/>
@@ -38,16 +38,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="121">
   <si>
     <t>ΠΕΡΙΦΕΡΕΙΑ</t>
   </si>
   <si>
     <t>ΠΕΡΙΦΕΡΕΙΑΚΗ ΕΝΟΤΗΤΑ</t>
-  </si>
-  <si>
-    <t>ΚΥΚΛΟΣ ΕΡΓΑΣΙΩΝ
-(σε ευρώ)</t>
   </si>
   <si>
     <t>ΑΝΑΤΟΛΙΚΗΣ ΜΑΚΕΔΟΝΙΑΣ ΚΑΙ ΘΡΑΚΗΣ</t>
@@ -850,7 +846,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -904,40 +900,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -947,6 +912,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -955,6 +926,35 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1271,47 +1271,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCD044BA-E01C-4A25-96E6-3460B990F4C5}">
   <dimension ref="A1:K78"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="5" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="5" width="17.33203125" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" customWidth="1"/>
+    <col min="9" max="9" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-    </row>
-    <row r="3" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+    <row r="1" spans="1:9" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+    </row>
+    <row r="3" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="30"/>
-    </row>
-    <row r="4" spans="1:8" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
+      <c r="C3" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="36"/>
+    </row>
+    <row r="4" spans="1:9" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
       <c r="C4" s="5">
         <v>2019</v>
       </c>
@@ -1330,13 +1332,16 @@
       <c r="H4" s="5">
         <v>2024</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="I4" s="5">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="37" t="s">
         <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>4</v>
       </c>
       <c r="C5" s="9">
         <v>33266</v>
@@ -1356,13 +1361,16 @@
       <c r="H5" s="9">
         <v>50718</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" s="9">
+        <v>48551</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>6</v>
       </c>
       <c r="C6" s="9">
         <v>26730</v>
@@ -1382,13 +1390,16 @@
       <c r="H6" s="9">
         <v>41373</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="9">
+        <v>36293</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="9">
         <v>47704</v>
@@ -1408,13 +1419,16 @@
       <c r="H7" s="9">
         <v>82209</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="9">
+        <v>80777</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="9">
         <v>23758</v>
@@ -1434,13 +1448,16 @@
       <c r="H8" s="9">
         <v>45707</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" s="9">
+        <v>47859</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="9">
         <v>52913</v>
@@ -1460,13 +1477,16 @@
       <c r="H9" s="9">
         <v>95832</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" s="9">
+        <v>88952</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="9">
         <v>32687</v>
@@ -1486,13 +1506,16 @@
       <c r="H10" s="9">
         <v>50496</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="9">
+        <v>50822</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="C11" s="9">
         <v>537967</v>
@@ -1512,13 +1535,16 @@
       <c r="H11" s="9">
         <v>907947</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="9">
+        <v>852053</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="9">
         <v>33724</v>
@@ -1538,13 +1564,16 @@
       <c r="H12" s="9">
         <v>60695</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="9">
+        <v>57247</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="9">
         <v>17135</v>
@@ -1564,13 +1593,16 @@
       <c r="H13" s="9">
         <v>27346</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="9">
+        <v>26214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="9">
         <v>29740</v>
@@ -1590,13 +1622,16 @@
       <c r="H14" s="9">
         <v>56479</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="9">
+        <v>54603</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9">
         <v>70120</v>
@@ -1616,13 +1651,16 @@
       <c r="H15" s="9">
         <v>113991</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="9">
+        <v>107732</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="9">
         <v>35099</v>
@@ -1642,13 +1680,16 @@
       <c r="H16" s="9">
         <v>57694</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" s="9">
+        <v>54004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="9">
         <v>108052</v>
@@ -1668,13 +1709,16 @@
       <c r="H17" s="9">
         <v>204550</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" s="9">
+        <v>200997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="C18" s="9">
         <v>37798</v>
@@ -1694,13 +1738,16 @@
       <c r="H18" s="9">
         <v>63277</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="9">
+        <v>59429</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" s="9">
         <v>9075</v>
@@ -1720,13 +1767,16 @@
       <c r="H19" s="9">
         <v>12718</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" s="9">
+        <v>11302</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" s="9">
         <v>11001</v>
@@ -1746,13 +1796,16 @@
       <c r="H20" s="9">
         <v>18260</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" s="9">
+        <v>16813</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="9">
         <v>11527</v>
@@ -1772,13 +1825,16 @@
       <c r="H21" s="9">
         <v>22211</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" s="9">
+        <v>21323</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="C22" s="9">
         <v>78166</v>
@@ -1798,13 +1854,16 @@
       <c r="H22" s="9">
         <v>137316</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22" s="9">
+        <v>129631</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="9">
         <v>17647</v>
@@ -1824,13 +1883,16 @@
       <c r="H23" s="9">
         <v>24737</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23" s="9">
+        <v>22122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" s="9">
         <v>23904</v>
@@ -1850,13 +1912,16 @@
       <c r="H24" s="9">
         <v>39059</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" s="9">
+        <v>39273</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="9">
         <v>37445</v>
@@ -1876,13 +1941,16 @@
       <c r="H25" s="9">
         <v>67669</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" s="9">
+        <v>68408</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="C26" s="9">
         <v>89997</v>
@@ -1902,13 +1970,16 @@
       <c r="H26" s="9">
         <v>159072</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" s="9">
+        <v>151201</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="9">
         <v>22928</v>
@@ -1928,13 +1999,16 @@
       <c r="H27" s="9">
         <v>36565</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="9">
+        <v>36331</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="9">
         <v>77956</v>
@@ -1954,13 +2028,16 @@
       <c r="H28" s="9">
         <v>139327</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" s="9">
+        <v>131959</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" s="9">
         <v>37078</v>
@@ -1980,13 +2057,16 @@
       <c r="H29" s="9">
         <v>60564</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="9">
+        <v>60693</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="9">
         <v>43964</v>
@@ -2006,13 +2086,16 @@
       <c r="H30" s="9">
         <v>70250</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="9">
+        <v>67884</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="C31" s="9">
         <v>46381</v>
@@ -2032,13 +2115,16 @@
       <c r="H31" s="9">
         <v>79120</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="9">
+        <v>77035</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" s="9">
         <v>30926</v>
@@ -2058,13 +2144,16 @@
       <c r="H32" s="9">
         <v>59970</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="9">
+        <v>57930</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33" s="9">
         <v>86331</v>
@@ -2084,13 +2173,16 @@
       <c r="H33" s="9">
         <v>155630</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="9">
+        <v>152683</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" s="9">
         <v>4313</v>
@@ -2110,13 +2202,16 @@
       <c r="H34" s="9">
         <v>7949</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="9">
+        <v>8005</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C35" s="9">
         <v>17529</v>
@@ -2136,13 +2231,16 @@
       <c r="H35" s="9">
         <v>31002</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="9">
+        <v>31076</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="C36" s="9">
         <v>119656</v>
@@ -2162,13 +2260,16 @@
       <c r="H36" s="9">
         <v>243900</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" s="9">
+        <v>252815</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37" s="9">
         <v>60646</v>
@@ -2188,13 +2289,16 @@
       <c r="H37" s="9">
         <v>134262</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37" s="9">
+        <v>131908</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" s="9">
         <v>3244</v>
@@ -2214,13 +2318,16 @@
       <c r="H38" s="9">
         <v>8341</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" s="9">
+        <v>8310</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" s="9">
         <v>46293</v>
@@ -2240,13 +2347,16 @@
       <c r="H39" s="9">
         <v>75940</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" s="9">
+        <v>75804</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="9">
         <v>36510</v>
@@ -2266,13 +2376,16 @@
       <c r="H40" s="9">
         <v>67048</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="9">
+        <v>69837</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="C41" s="9">
         <v>112074</v>
@@ -2292,13 +2405,16 @@
       <c r="H41" s="9">
         <v>198319</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" s="9">
+        <v>184565</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C42" s="9">
         <v>67016</v>
@@ -2318,13 +2434,16 @@
       <c r="H42" s="9">
         <v>115566</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42" s="9">
+        <v>113619</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" s="9">
         <v>39788</v>
@@ -2344,13 +2463,16 @@
       <c r="H43" s="9">
         <v>69028</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" s="9">
+        <v>72119</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="C44" s="9">
         <v>34250</v>
@@ -2370,13 +2492,16 @@
       <c r="H44" s="9">
         <v>57027</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" s="9">
+        <v>57341</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C45" s="9">
         <v>66871</v>
@@ -2396,13 +2521,16 @@
       <c r="H45" s="9">
         <v>110714</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I45" s="9">
+        <v>105002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="9">
         <v>76101</v>
@@ -2422,13 +2550,16 @@
       <c r="H46" s="9">
         <v>138523</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46" s="9">
+        <v>137778</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C47" s="9">
         <v>41572</v>
@@ -2448,13 +2579,16 @@
       <c r="H47" s="9">
         <v>75124</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" s="9">
+        <v>71457</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C48" s="9">
         <v>91228</v>
@@ -2474,13 +2608,16 @@
       <c r="H48" s="9">
         <v>163596</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48" s="9">
+        <v>150370</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C49" s="9">
         <v>2447373</v>
@@ -2500,22 +2637,25 @@
       <c r="H49" s="9">
         <v>4464743</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I49" s="9">
+        <v>4302789</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="C50" s="9">
         <v>54890</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F50" s="9">
         <v>60976</v>
@@ -2526,13 +2666,16 @@
       <c r="H50" s="9">
         <v>85927</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I50" s="9">
+        <v>82391</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C51" s="9">
         <v>3901</v>
@@ -2552,13 +2695,16 @@
       <c r="H51" s="9">
         <v>9087</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I51" s="9">
+        <v>8376</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="9">
         <v>8125</v>
@@ -2578,13 +2724,16 @@
       <c r="H52" s="9">
         <v>19049</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52" s="9">
+        <v>19181</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C53" s="9">
         <v>23516</v>
@@ -2604,13 +2753,16 @@
       <c r="H53" s="9">
         <v>47262</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I53" s="9">
+        <v>46424</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" s="9">
         <v>29591</v>
@@ -2630,13 +2782,16 @@
       <c r="H54" s="9">
         <v>56685</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I54" s="9">
+        <v>56739</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="C55" s="9">
         <v>19920</v>
@@ -2656,13 +2811,16 @@
       <c r="H55" s="9">
         <v>36931</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I55" s="9">
+        <v>34108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56" s="9">
         <v>9073</v>
@@ -2682,13 +2840,16 @@
       <c r="H56" s="9">
         <v>14683</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I56" s="9">
+        <v>15438</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57" s="9">
         <v>135543</v>
@@ -2708,13 +2869,16 @@
       <c r="H57" s="9">
         <v>212406</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I57" s="9">
+        <v>179476</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" s="9">
         <v>20463</v>
@@ -2734,13 +2898,16 @@
       <c r="H58" s="9">
         <v>43784</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I58" s="9">
+        <v>45415</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C59" s="9">
         <v>9893</v>
@@ -2760,13 +2927,16 @@
       <c r="H59" s="9">
         <v>18418</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I59" s="9">
+        <v>16302</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C60" s="9">
         <v>7347</v>
@@ -2786,13 +2956,16 @@
       <c r="H60" s="9">
         <v>16138</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I60" s="9">
+        <v>16735</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C61" s="9">
         <v>48520</v>
@@ -2812,13 +2985,16 @@
       <c r="H61" s="9">
         <v>108640</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I61" s="9">
+        <v>103905</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C62" s="9">
         <v>23211</v>
@@ -2838,13 +3014,16 @@
       <c r="H62" s="9">
         <v>52175</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I62" s="9">
+        <v>52251</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C63" s="9">
         <v>131048</v>
@@ -2864,13 +3043,16 @@
       <c r="H63" s="9">
         <v>182634</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I63" s="9">
+        <v>174656</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C64" s="9">
         <v>40249</v>
@@ -2890,13 +3072,16 @@
       <c r="H64" s="9">
         <v>78121</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I64" s="9">
+        <v>77179</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65" s="9">
         <v>50451</v>
@@ -2916,13 +3101,16 @@
       <c r="H65" s="9">
         <v>108845</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I65" s="9">
+        <v>105286</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C66" s="9">
         <v>144652</v>
@@ -2942,13 +3130,16 @@
       <c r="H66" s="9">
         <v>288283</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I66" s="9">
+        <v>286789</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C67" s="9">
         <v>12656</v>
@@ -2968,13 +3159,16 @@
       <c r="H67" s="9">
         <v>27711</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I67" s="9">
+        <v>25423</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="C68" s="9">
         <v>162230</v>
@@ -2994,13 +3188,16 @@
       <c r="H68" s="9">
         <v>298707</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I68" s="9">
+        <v>302102</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C69" s="9">
         <v>50697</v>
@@ -3020,13 +3217,16 @@
       <c r="H69" s="9">
         <v>91449</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I69" s="9">
+        <v>84993</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C70" s="9">
         <v>79883</v>
@@ -3046,13 +3246,16 @@
       <c r="H70" s="9">
         <v>140923</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I70" s="9">
+        <v>141280</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C71" s="9">
         <v>152035</v>
@@ -3072,12 +3275,15 @@
       <c r="H71" s="9">
         <v>277510</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="B72" s="26"/>
+      <c r="I71" s="9">
+        <v>277380</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" s="32"/>
       <c r="C72" s="10">
         <v>6193377</v>
       </c>
@@ -3096,38 +3302,41 @@
       <c r="H72" s="10">
         <v>11117232</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="B74" s="27"/>
-    </row>
-    <row r="75" spans="1:11" ht="27.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B75" s="21"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-    </row>
-    <row r="76" spans="1:11" ht="25.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="21"/>
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I72" s="10">
+        <v>10734747</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74" s="28"/>
+    </row>
+    <row r="75" spans="1:11" ht="27.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B75" s="29"/>
+      <c r="C75" s="29"/>
+      <c r="D75" s="29"/>
+      <c r="E75" s="29"/>
+      <c r="F75" s="29"/>
+      <c r="G75" s="29"/>
+      <c r="H75" s="29"/>
+    </row>
+    <row r="76" spans="1:11" ht="25.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="29"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+      <c r="D76" s="29"/>
+      <c r="E76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="29"/>
+      <c r="H76" s="29"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B77" s="23"/>
       <c r="C77" s="23"/>
@@ -3136,16 +3345,16 @@
       <c r="F77" s="23"/>
       <c r="G77" s="23"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="B78" s="22"/>
-      <c r="C78" s="22"/>
-      <c r="D78" s="22"/>
-      <c r="E78" s="22"/>
-      <c r="F78" s="22"/>
-      <c r="G78" s="22"/>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="B78" s="24"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
@@ -3161,7 +3370,7 @@
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3171,185 +3380,185 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A096C99-39EB-4BA7-BE0B-680796F89026}">
   <dimension ref="A1:AD79"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
-    <col min="3" max="26" width="12.28515625" customWidth="1"/>
-    <col min="27" max="27" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="30.5546875" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="26" width="12.33203125" customWidth="1"/>
+    <col min="27" max="27" width="11.109375" customWidth="1"/>
     <col min="28" max="30" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17"/>
       <c r="B1" s="18"/>
-      <c r="C1" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
-    </row>
-    <row r="3" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="C1" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
+      <c r="V1" s="19"/>
+      <c r="W1" s="19"/>
+      <c r="X1" s="19"/>
+      <c r="Y1" s="19"/>
+      <c r="Z1" s="19"/>
+      <c r="AA1" s="19"/>
+      <c r="AB1" s="19"/>
+      <c r="AC1" s="19"/>
+      <c r="AD1" s="19"/>
+    </row>
+    <row r="3" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="32"/>
-      <c r="Z3" s="32"/>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="33"/>
-    </row>
-    <row r="4" spans="1:30" s="12" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
-      <c r="B4" s="34"/>
+      <c r="C3" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="21"/>
+      <c r="AB3" s="21"/>
+      <c r="AC3" s="21"/>
+      <c r="AD3" s="22"/>
+    </row>
+    <row r="4" spans="1:30" s="12" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
       <c r="C4" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="E4" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="F4" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="G4" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="H4" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="I4" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="J4" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="K4" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="L4" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="L4" s="16" t="s">
+      <c r="M4" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="M4" s="16" t="s">
+      <c r="N4" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="N4" s="16" t="s">
+      <c r="O4" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="O4" s="16" t="s">
+      <c r="P4" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="P4" s="16" t="s">
+      <c r="Q4" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="Q4" s="16" t="s">
+      <c r="R4" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="R4" s="16" t="s">
-        <v>101</v>
-      </c>
       <c r="S4" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="T4" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="T4" s="16" t="s">
+      <c r="U4" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="U4" s="16" t="s">
+      <c r="V4" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="V4" s="16" t="s">
+      <c r="W4" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="W4" s="16" t="s">
+      <c r="X4" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="X4" s="16" t="s">
+      <c r="Y4" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="Y4" s="16" t="s">
+      <c r="Z4" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="Z4" s="16" t="s">
-        <v>113</v>
-      </c>
       <c r="AA4" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AB4" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC4" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="AC4" s="16" t="s">
+      <c r="AD4" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="AD4" s="16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="C5" s="13">
         <v>6973</v>
@@ -3406,7 +3615,7 @@
         <v>11579</v>
       </c>
       <c r="U5" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V5" s="13">
         <v>12716</v>
@@ -3429,15 +3638,19 @@
       <c r="AB5" s="13">
         <v>12647</v>
       </c>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC5" s="13">
+        <v>13615</v>
+      </c>
+      <c r="AD5" s="13">
+        <v>11351</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="C6" s="13">
         <v>4669</v>
@@ -3517,15 +3730,19 @@
       <c r="AB6" s="13">
         <v>8736</v>
       </c>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC6" s="13">
+        <v>9856</v>
+      </c>
+      <c r="AD6" s="13">
+        <v>9366</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="13">
         <v>8332</v>
@@ -3605,15 +3822,19 @@
       <c r="AB7" s="13">
         <v>19982</v>
       </c>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC7" s="13">
+        <v>27814</v>
+      </c>
+      <c r="AD7" s="13">
+        <v>17653</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="13">
         <v>592</v>
@@ -3693,15 +3914,19 @@
       <c r="AB8" s="13">
         <v>10512</v>
       </c>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC8" s="13">
+        <v>34166</v>
+      </c>
+      <c r="AD8" s="13">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="13">
         <v>7404</v>
@@ -3781,15 +4006,19 @@
       <c r="AB9" s="13">
         <v>21355</v>
       </c>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC9" s="13">
+        <v>39791</v>
+      </c>
+      <c r="AD9" s="13">
+        <v>14064</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="13">
         <v>6154</v>
@@ -3869,15 +4098,19 @@
       <c r="AB10" s="13">
         <v>12403</v>
       </c>
-      <c r="AC10" s="13"/>
-      <c r="AD10" s="13"/>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC10" s="13">
+        <v>15192</v>
+      </c>
+      <c r="AD10" s="13">
+        <v>11978</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="C11" s="13">
         <v>111947</v>
@@ -3957,15 +4190,19 @@
       <c r="AB11" s="13">
         <v>218718</v>
       </c>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC11" s="13">
+        <v>209414</v>
+      </c>
+      <c r="AD11" s="13">
+        <v>218917</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="13">
         <v>6703</v>
@@ -4031,7 +4268,7 @@
         <v>14409</v>
       </c>
       <c r="X12" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y12" s="13">
         <v>16072</v>
@@ -4045,15 +4282,19 @@
       <c r="AB12" s="13">
         <v>13593</v>
       </c>
-      <c r="AC12" s="13"/>
-      <c r="AD12" s="13"/>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC12" s="13">
+        <v>15397</v>
+      </c>
+      <c r="AD12" s="13">
+        <v>15095</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="13">
         <v>3183</v>
@@ -4133,15 +4374,19 @@
       <c r="AB13" s="13">
         <v>6612</v>
       </c>
-      <c r="AC13" s="13"/>
-      <c r="AD13" s="13"/>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC13" s="13">
+        <v>8405</v>
+      </c>
+      <c r="AD13" s="13">
+        <v>6108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="13">
         <v>5361</v>
@@ -4221,15 +4466,19 @@
       <c r="AB14" s="13">
         <v>12071</v>
       </c>
-      <c r="AC14" s="13"/>
-      <c r="AD14" s="13"/>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC14" s="13">
+        <v>15157</v>
+      </c>
+      <c r="AD14" s="13">
+        <v>14995</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="13">
         <v>9621</v>
@@ -4309,15 +4558,19 @@
       <c r="AB15" s="13">
         <v>25995</v>
       </c>
-      <c r="AC15" s="13"/>
-      <c r="AD15" s="13"/>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC15" s="13">
+        <v>49945</v>
+      </c>
+      <c r="AD15" s="13">
+        <v>16735</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="13">
         <v>6607</v>
@@ -4374,7 +4627,7 @@
         <v>14902</v>
       </c>
       <c r="U16" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V16" s="13">
         <v>17085</v>
@@ -4397,15 +4650,19 @@
       <c r="AB16" s="13">
         <v>13292</v>
       </c>
-      <c r="AC16" s="13"/>
-      <c r="AD16" s="13"/>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC16" s="13">
+        <v>14620</v>
+      </c>
+      <c r="AD16" s="13">
+        <v>13789</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="13">
         <v>5484</v>
@@ -4485,15 +4742,19 @@
       <c r="AB17" s="13">
         <v>48869</v>
       </c>
-      <c r="AC17" s="13"/>
-      <c r="AD17" s="13"/>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC17" s="13">
+        <v>118977</v>
+      </c>
+      <c r="AD17" s="13">
+        <v>17518</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="C18" s="13">
         <v>7978</v>
@@ -4573,15 +4834,19 @@
       <c r="AB18" s="13">
         <v>14906</v>
       </c>
-      <c r="AC18" s="13"/>
-      <c r="AD18" s="13"/>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC18" s="13">
+        <v>15696</v>
+      </c>
+      <c r="AD18" s="13">
+        <v>14710</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" s="13">
         <v>1590</v>
@@ -4661,15 +4926,19 @@
       <c r="AB19" s="13">
         <v>2588</v>
       </c>
-      <c r="AC19" s="13"/>
-      <c r="AD19" s="13"/>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC19" s="13">
+        <v>3439</v>
+      </c>
+      <c r="AD19" s="13">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" s="13">
         <v>2146</v>
@@ -4749,15 +5018,19 @@
       <c r="AB20" s="13">
         <v>4043</v>
       </c>
-      <c r="AC20" s="13"/>
-      <c r="AD20" s="13"/>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC20" s="13">
+        <v>4429</v>
+      </c>
+      <c r="AD20" s="13">
+        <v>4133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="13">
         <v>2316</v>
@@ -4837,15 +5110,19 @@
       <c r="AB21" s="13">
         <v>5123</v>
       </c>
-      <c r="AC21" s="13"/>
-      <c r="AD21" s="13"/>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC21" s="13">
+        <v>5448</v>
+      </c>
+      <c r="AD21" s="13">
+        <v>5391</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="C22" s="13">
         <v>16036</v>
@@ -4925,15 +5202,19 @@
       <c r="AB22" s="13">
         <v>31888</v>
       </c>
-      <c r="AC22" s="13"/>
-      <c r="AD22" s="13"/>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC22" s="13">
+        <v>35511</v>
+      </c>
+      <c r="AD22" s="13">
+        <v>31710</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="13">
         <v>3397</v>
@@ -4990,7 +5271,7 @@
         <v>6461</v>
       </c>
       <c r="U23" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V23" s="13">
         <v>6679</v>
@@ -5013,15 +5294,19 @@
       <c r="AB23" s="13">
         <v>5759</v>
       </c>
-      <c r="AC23" s="13"/>
-      <c r="AD23" s="13"/>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC23" s="13">
+        <v>6098</v>
+      </c>
+      <c r="AD23" s="13">
+        <v>5437</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" s="13">
         <v>2753</v>
@@ -5101,15 +5386,19 @@
       <c r="AB24" s="13">
         <v>9137</v>
       </c>
-      <c r="AC24" s="13"/>
-      <c r="AD24" s="13"/>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC24" s="13">
+        <v>19684</v>
+      </c>
+      <c r="AD24" s="13">
+        <v>5947</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="13">
         <v>3138</v>
@@ -5189,15 +5478,19 @@
       <c r="AB25" s="13">
         <v>16716</v>
       </c>
-      <c r="AC25" s="13"/>
-      <c r="AD25" s="13"/>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC25" s="13">
+        <v>38606</v>
+      </c>
+      <c r="AD25" s="13">
+        <v>6922</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="C26" s="13">
         <v>17488</v>
@@ -5277,15 +5570,19 @@
       <c r="AB26" s="13">
         <v>37268</v>
       </c>
-      <c r="AC26" s="13"/>
-      <c r="AD26" s="13"/>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC26" s="13">
+        <v>40961</v>
+      </c>
+      <c r="AD26" s="13">
+        <v>38210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="13">
         <v>4635</v>
@@ -5365,15 +5662,19 @@
       <c r="AB27" s="13">
         <v>8975</v>
       </c>
-      <c r="AC27" s="13"/>
-      <c r="AD27" s="13"/>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC27" s="13">
+        <v>9238</v>
+      </c>
+      <c r="AD27" s="13">
+        <v>9923</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="13">
         <v>13292</v>
@@ -5453,15 +5754,19 @@
       <c r="AB28" s="13">
         <v>30794</v>
       </c>
-      <c r="AC28" s="13"/>
-      <c r="AD28" s="13"/>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC28" s="13">
+        <v>44865</v>
+      </c>
+      <c r="AD28" s="13">
+        <v>30364</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" s="13">
         <v>1110</v>
@@ -5541,15 +5846,19 @@
       <c r="AB29" s="13">
         <v>14275</v>
       </c>
-      <c r="AC29" s="13"/>
-      <c r="AD29" s="13"/>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC29" s="13">
+        <v>42397</v>
+      </c>
+      <c r="AD29" s="13">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C30" s="13">
         <v>8178</v>
@@ -5629,15 +5938,19 @@
       <c r="AB30" s="13">
         <v>16435</v>
       </c>
-      <c r="AC30" s="13"/>
-      <c r="AD30" s="13"/>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC30" s="13">
+        <v>17744</v>
+      </c>
+      <c r="AD30" s="13">
+        <v>19221</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="C31" s="13">
         <v>7538</v>
@@ -5717,15 +6030,19 @@
       <c r="AB31" s="13">
         <v>19467</v>
       </c>
-      <c r="AC31" s="13"/>
-      <c r="AD31" s="13"/>
-    </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC31" s="13">
+        <v>24773</v>
+      </c>
+      <c r="AD31" s="13">
+        <v>17429</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" s="13">
         <v>6467</v>
@@ -5805,15 +6122,19 @@
       <c r="AB32" s="13">
         <v>13517</v>
       </c>
-      <c r="AC32" s="13"/>
-      <c r="AD32" s="13"/>
-    </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC32" s="13">
+        <v>15086</v>
+      </c>
+      <c r="AD32" s="13">
+        <v>14887</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33" s="13">
         <v>11730</v>
@@ -5893,15 +6214,19 @@
       <c r="AB33" s="13">
         <v>36321</v>
       </c>
-      <c r="AC33" s="13"/>
-      <c r="AD33" s="13"/>
-    </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC33" s="13">
+        <v>61435</v>
+      </c>
+      <c r="AD33" s="13">
+        <v>29044</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" s="13">
         <v>706</v>
@@ -5958,7 +6283,7 @@
         <v>1463</v>
       </c>
       <c r="U34" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V34" s="13">
         <v>2081</v>
@@ -5981,15 +6306,19 @@
       <c r="AB34" s="13">
         <v>1665</v>
       </c>
-      <c r="AC34" s="13"/>
-      <c r="AD34" s="13"/>
-    </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC34" s="13">
+        <v>2473</v>
+      </c>
+      <c r="AD34" s="13">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C35" s="13">
         <v>2772</v>
@@ -6069,15 +6398,19 @@
       <c r="AB35" s="13">
         <v>7765</v>
       </c>
-      <c r="AC35" s="13"/>
-      <c r="AD35" s="13"/>
-    </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC35" s="13">
+        <v>12055</v>
+      </c>
+      <c r="AD35" s="13">
+        <v>5768</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="C36" s="13">
         <v>6545</v>
@@ -6157,15 +6490,19 @@
       <c r="AB36" s="13">
         <v>68040</v>
       </c>
-      <c r="AC36" s="13"/>
-      <c r="AD36" s="13"/>
-    </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC36" s="13">
+        <v>144048</v>
+      </c>
+      <c r="AD36" s="13">
+        <v>26981</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37" s="13">
         <v>2171</v>
@@ -6219,7 +6556,7 @@
         <v>5167</v>
       </c>
       <c r="T37" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U37" s="13">
         <v>82349</v>
@@ -6245,15 +6582,19 @@
       <c r="AB37" s="13">
         <v>34590</v>
       </c>
-      <c r="AC37" s="13"/>
-      <c r="AD37" s="13"/>
-    </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC37" s="13">
+        <v>81261</v>
+      </c>
+      <c r="AD37" s="13">
+        <v>10968</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" s="13">
         <v>64</v>
@@ -6333,15 +6674,19 @@
       <c r="AB38" s="13">
         <v>1867</v>
       </c>
-      <c r="AC38" s="13"/>
-      <c r="AD38" s="13"/>
-    </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC38" s="13">
+        <v>5847</v>
+      </c>
+      <c r="AD38" s="13">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" s="13">
         <v>1831</v>
@@ -6421,15 +6766,19 @@
       <c r="AB39" s="13">
         <v>19255</v>
       </c>
-      <c r="AC39" s="13"/>
-      <c r="AD39" s="13"/>
-    </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC39" s="13">
+        <v>47302</v>
+      </c>
+      <c r="AD39" s="13">
+        <v>5773</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="13">
         <v>1370</v>
@@ -6509,15 +6858,19 @@
       <c r="AB40" s="13">
         <v>16055</v>
       </c>
-      <c r="AC40" s="13"/>
-      <c r="AD40" s="13"/>
-    </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC40" s="13">
+        <v>46475</v>
+      </c>
+      <c r="AD40" s="13">
+        <v>4731</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="C41" s="13">
         <v>22924</v>
@@ -6597,15 +6950,19 @@
       <c r="AB41" s="13">
         <v>45422</v>
       </c>
-      <c r="AC41" s="13"/>
-      <c r="AD41" s="13"/>
-    </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC41" s="13">
+        <v>52374</v>
+      </c>
+      <c r="AD41" s="13">
+        <v>42753</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C42" s="13">
         <v>11966</v>
@@ -6685,15 +7042,19 @@
       <c r="AB42" s="13">
         <v>27917</v>
       </c>
-      <c r="AC42" s="13"/>
-      <c r="AD42" s="13"/>
-    </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC42" s="13">
+        <v>36702</v>
+      </c>
+      <c r="AD42" s="13">
+        <v>26299</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" s="13">
         <v>5702</v>
@@ -6773,15 +7134,19 @@
       <c r="AB43" s="13">
         <v>17763</v>
       </c>
-      <c r="AC43" s="13"/>
-      <c r="AD43" s="13"/>
-    </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC43" s="13">
+        <v>26742</v>
+      </c>
+      <c r="AD43" s="13">
+        <v>15176</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="C44" s="13">
         <v>5795</v>
@@ -6861,15 +7226,19 @@
       <c r="AB44" s="13">
         <v>13110</v>
       </c>
-      <c r="AC44" s="13"/>
-      <c r="AD44" s="13"/>
-    </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC44" s="13">
+        <v>19392</v>
+      </c>
+      <c r="AD44" s="13">
+        <v>13522</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C45" s="13">
         <v>9922</v>
@@ -6949,15 +7318,19 @@
       <c r="AB45" s="13">
         <v>28550</v>
       </c>
-      <c r="AC45" s="13"/>
-      <c r="AD45" s="13"/>
-    </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC45" s="13">
+        <v>41783</v>
+      </c>
+      <c r="AD45" s="13">
+        <v>18400</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="13">
         <v>12161</v>
@@ -7005,13 +7378,13 @@
         <v>45889</v>
       </c>
       <c r="R46" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S46" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T46" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U46" s="13">
         <v>53628</v>
@@ -7037,15 +7410,19 @@
       <c r="AB46" s="13">
         <v>34470</v>
       </c>
-      <c r="AC46" s="13"/>
-      <c r="AD46" s="13"/>
-    </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC46" s="13">
+        <v>47118</v>
+      </c>
+      <c r="AD46" s="13">
+        <v>30519</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C47" s="13">
         <v>5194</v>
@@ -7125,15 +7502,19 @@
       <c r="AB47" s="13">
         <v>16905</v>
       </c>
-      <c r="AC47" s="13"/>
-      <c r="AD47" s="13"/>
-    </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC47" s="13">
+        <v>30874</v>
+      </c>
+      <c r="AD47" s="13">
+        <v>12823</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C48" s="13">
         <v>11217</v>
@@ -7213,15 +7594,19 @@
       <c r="AB48" s="13">
         <v>36879</v>
       </c>
-      <c r="AC48" s="13"/>
-      <c r="AD48" s="13"/>
-    </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC48" s="13">
+        <v>63576</v>
+      </c>
+      <c r="AD48" s="13">
+        <v>25823</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C49" s="13">
         <v>466406</v>
@@ -7301,15 +7686,19 @@
       <c r="AB49" s="13">
         <v>1117919</v>
       </c>
-      <c r="AC49" s="13"/>
-      <c r="AD49" s="13"/>
-    </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC49" s="13">
+        <v>1232354</v>
+      </c>
+      <c r="AD49" s="13">
+        <v>1035955</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="C50" s="13">
         <v>6636</v>
@@ -7324,31 +7713,31 @@
         <v>14243</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L50" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M50" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O50" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P50" s="13">
         <v>13797</v>
@@ -7369,7 +7758,7 @@
         <v>32338</v>
       </c>
       <c r="V50" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W50" s="13">
         <v>14993</v>
@@ -7389,15 +7778,19 @@
       <c r="AB50" s="13">
         <v>20760</v>
       </c>
-      <c r="AC50" s="13"/>
-      <c r="AD50" s="13"/>
-    </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC50" s="13">
+        <v>34414</v>
+      </c>
+      <c r="AD50" s="13">
+        <v>13748</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C51" s="13">
         <v>152</v>
@@ -7457,7 +7850,7 @@
         <v>5574</v>
       </c>
       <c r="V51" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W51" s="13">
         <v>492</v>
@@ -7477,15 +7870,19 @@
       <c r="AB51" s="13">
         <v>1405</v>
       </c>
-      <c r="AC51" s="13"/>
-      <c r="AD51" s="13"/>
-    </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC51" s="13">
+        <v>5845</v>
+      </c>
+      <c r="AD51" s="13">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="13">
         <v>650</v>
@@ -7539,7 +7936,7 @@
         <v>1293</v>
       </c>
       <c r="T52" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U52" s="13">
         <v>9311</v>
@@ -7554,7 +7951,7 @@
         <v>3025</v>
       </c>
       <c r="Y52" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Z52" s="13">
         <v>1598</v>
@@ -7565,15 +7962,19 @@
       <c r="AB52" s="13">
         <v>3331</v>
       </c>
-      <c r="AC52" s="13"/>
-      <c r="AD52" s="13"/>
-    </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC52" s="13">
+        <v>12954</v>
+      </c>
+      <c r="AD52" s="13">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C53" s="13">
         <v>1813</v>
@@ -7653,15 +8054,19 @@
       <c r="AB53" s="13">
         <v>11073</v>
       </c>
-      <c r="AC53" s="13"/>
-      <c r="AD53" s="13"/>
-    </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC53" s="13">
+        <v>26943</v>
+      </c>
+      <c r="AD53" s="13">
+        <v>5079</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" s="13">
         <v>4549</v>
@@ -7741,15 +8146,19 @@
       <c r="AB54" s="13">
         <v>12543</v>
       </c>
-      <c r="AC54" s="13"/>
-      <c r="AD54" s="13"/>
-    </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC54" s="13">
+        <v>24989</v>
+      </c>
+      <c r="AD54" s="13">
+        <v>10297</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="C55" s="13">
         <v>1651</v>
@@ -7809,7 +8218,7 @@
         <v>19472</v>
       </c>
       <c r="V55" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W55" s="13">
         <v>4208</v>
@@ -7829,15 +8238,19 @@
       <c r="AB55" s="13">
         <v>8455</v>
       </c>
-      <c r="AC55" s="13"/>
-      <c r="AD55" s="13"/>
-    </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC55" s="13">
+        <v>17751</v>
+      </c>
+      <c r="AD55" s="13">
+        <v>4333</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56" s="13">
         <v>376</v>
@@ -7885,7 +8298,7 @@
         <v>10015</v>
       </c>
       <c r="R56" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S56" s="13">
         <v>669</v>
@@ -7917,15 +8330,19 @@
       <c r="AB56" s="13">
         <v>3148</v>
       </c>
-      <c r="AC56" s="13"/>
-      <c r="AD56" s="13"/>
-    </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC56" s="13">
+        <v>10565</v>
+      </c>
+      <c r="AD56" s="13">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57" s="13">
         <v>3286</v>
@@ -7982,7 +8399,7 @@
         <v>68314</v>
       </c>
       <c r="U57" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V57" s="13">
         <v>26363</v>
@@ -8005,15 +8422,19 @@
       <c r="AB57" s="13">
         <v>51422</v>
       </c>
-      <c r="AC57" s="13"/>
-      <c r="AD57" s="13"/>
-    </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC57" s="13">
+        <v>99826</v>
+      </c>
+      <c r="AD57" s="13">
+        <v>24116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" s="13">
         <v>1115</v>
@@ -8093,15 +8514,19 @@
       <c r="AB58" s="13">
         <v>9727</v>
       </c>
-      <c r="AC58" s="13"/>
-      <c r="AD58" s="13"/>
-    </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC58" s="13">
+        <v>27120</v>
+      </c>
+      <c r="AD58" s="13">
+        <v>5534</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C59" s="13">
         <v>303</v>
@@ -8181,15 +8606,19 @@
       <c r="AB59" s="13">
         <v>3654</v>
       </c>
-      <c r="AC59" s="13"/>
-      <c r="AD59" s="13"/>
-    </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC59" s="13">
+        <v>10538</v>
+      </c>
+      <c r="AD59" s="13">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C60" s="13">
         <v>117</v>
@@ -8269,15 +8698,19 @@
       <c r="AB60" s="13">
         <v>3774</v>
       </c>
-      <c r="AC60" s="13"/>
-      <c r="AD60" s="13"/>
-    </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC60" s="13">
+        <v>11224</v>
+      </c>
+      <c r="AD60" s="13">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C61" s="13">
         <v>2705</v>
@@ -8357,15 +8790,19 @@
       <c r="AB61" s="13">
         <v>28435</v>
       </c>
-      <c r="AC61" s="13"/>
-      <c r="AD61" s="13"/>
-    </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC61" s="13">
+        <v>54855</v>
+      </c>
+      <c r="AD61" s="13">
+        <v>13921</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C62" s="13">
         <v>365</v>
@@ -8422,7 +8859,7 @@
         <v>9947</v>
       </c>
       <c r="U62" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V62" s="13">
         <v>3002</v>
@@ -8445,15 +8882,19 @@
       <c r="AB62" s="13">
         <v>12320</v>
       </c>
-      <c r="AC62" s="13"/>
-      <c r="AD62" s="13"/>
-    </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC62" s="13">
+        <v>36464</v>
+      </c>
+      <c r="AD62" s="13">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C63" s="13">
         <v>1460</v>
@@ -8533,15 +8974,19 @@
       <c r="AB63" s="13">
         <v>43975</v>
       </c>
-      <c r="AC63" s="13"/>
-      <c r="AD63" s="13"/>
-    </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC63" s="13">
+        <v>114345</v>
+      </c>
+      <c r="AD63" s="13">
+        <v>11763</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C64" s="13">
         <v>817</v>
@@ -8621,15 +9066,19 @@
       <c r="AB64" s="13">
         <v>16228</v>
       </c>
-      <c r="AC64" s="13"/>
-      <c r="AD64" s="13"/>
-    </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC64" s="13">
+        <v>53603</v>
+      </c>
+      <c r="AD64" s="13">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65" s="13">
         <v>740</v>
@@ -8656,7 +9105,7 @@
         <v>1970</v>
       </c>
       <c r="K65" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L65" s="13">
         <v>6955</v>
@@ -8709,15 +9158,19 @@
       <c r="AB65" s="13">
         <v>25250</v>
       </c>
-      <c r="AC65" s="13"/>
-      <c r="AD65" s="13"/>
-    </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC65" s="13">
+        <v>71544</v>
+      </c>
+      <c r="AD65" s="13">
+        <v>6304</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C66" s="13">
         <v>11698</v>
@@ -8771,7 +9224,7 @@
         <v>20090</v>
       </c>
       <c r="T66" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U66" s="13">
         <v>122737</v>
@@ -8797,15 +9250,19 @@
       <c r="AB66" s="13">
         <v>79080</v>
       </c>
-      <c r="AC66" s="13"/>
-      <c r="AD66" s="13"/>
-    </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC66" s="13">
+        <v>144050</v>
+      </c>
+      <c r="AD66" s="13">
+        <v>43218</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C67" s="13">
         <v>376</v>
@@ -8885,15 +9342,19 @@
       <c r="AB67" s="13">
         <v>5469</v>
       </c>
-      <c r="AC67" s="13"/>
-      <c r="AD67" s="13"/>
-    </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC67" s="13">
+        <v>16965</v>
+      </c>
+      <c r="AD67" s="13">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="C68" s="13">
         <v>21586</v>
@@ -8973,15 +9434,19 @@
       <c r="AB68" s="13">
         <v>77821</v>
       </c>
-      <c r="AC68" s="13"/>
-      <c r="AD68" s="13"/>
-    </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC68" s="13">
+        <v>119440</v>
+      </c>
+      <c r="AD68" s="13">
+        <v>59994</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C69" s="13">
         <v>4325</v>
@@ -9061,15 +9526,19 @@
       <c r="AB69" s="13">
         <v>22283</v>
       </c>
-      <c r="AC69" s="13"/>
-      <c r="AD69" s="13"/>
-    </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC69" s="13">
+        <v>41148</v>
+      </c>
+      <c r="AD69" s="13">
+        <v>13450</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C70" s="13">
         <v>9499</v>
@@ -9149,15 +9618,19 @@
       <c r="AB70" s="13">
         <v>36900</v>
       </c>
-      <c r="AC70" s="13"/>
-      <c r="AD70" s="13"/>
-    </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC70" s="13">
+        <v>61620</v>
+      </c>
+      <c r="AD70" s="13">
+        <v>25574</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C71" s="13">
         <v>13335</v>
@@ -9237,14 +9710,18 @@
       <c r="AB71" s="13">
         <v>72217</v>
       </c>
-      <c r="AC71" s="13"/>
-      <c r="AD71" s="13"/>
-    </row>
-    <row r="72" spans="1:30" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="B72" s="36"/>
+      <c r="AC71" s="13">
+        <v>132772</v>
+      </c>
+      <c r="AD71" s="13">
+        <v>45318</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30" ht="22.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72" s="27"/>
       <c r="C72" s="14">
         <v>947119</v>
       </c>
@@ -9323,10 +9800,14 @@
       <c r="AB72" s="14">
         <v>2729441</v>
       </c>
-      <c r="AC72" s="14"/>
-      <c r="AD72" s="14"/>
-    </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC72" s="14">
+        <v>3977114</v>
+      </c>
+      <c r="AD72" s="14">
+        <v>2184281</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.3">
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
       <c r="E73" s="11"/>
@@ -9348,11 +9829,11 @@
       <c r="U73" s="11"/>
       <c r="V73" s="11"/>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A74" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="B74" s="27"/>
+    <row r="74" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A74" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74" s="28"/>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
       <c r="E74" s="11"/>
@@ -9374,37 +9855,37 @@
       <c r="U74" s="11"/>
       <c r="V74" s="11"/>
     </row>
-    <row r="75" spans="1:30" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B75" s="21"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
+    <row r="75" spans="1:30" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="B75" s="29"/>
+      <c r="C75" s="29"/>
+      <c r="D75" s="29"/>
+      <c r="E75" s="29"/>
+      <c r="F75" s="29"/>
+      <c r="G75" s="29"/>
+      <c r="H75" s="29"/>
       <c r="I75" s="8"/>
       <c r="J75" s="8"/>
       <c r="K75" s="8"/>
     </row>
-    <row r="76" spans="1:30" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="21"/>
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
+    <row r="76" spans="1:30" ht="20.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="29"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+      <c r="D76" s="29"/>
+      <c r="E76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="29"/>
+      <c r="H76" s="29"/>
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
       <c r="K76" s="8"/>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A77" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B77" s="23"/>
       <c r="C77" s="23"/>
@@ -9420,9 +9901,9 @@
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A78" s="22" t="s">
-        <v>104</v>
+    <row r="78" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A78" s="24" t="s">
+        <v>103</v>
       </c>
       <c r="B78" s="23"/>
       <c r="C78" s="23"/>
@@ -9435,7 +9916,7 @@
       <c r="J78" s="23"/>
       <c r="K78" s="23"/>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.3">
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
